--- a/수가표_번역/C.수가표_PPT대조메모(국문).xlsx
+++ b/수가표_번역/C.수가표_PPT대조메모(국문).xlsx
@@ -1016,7 +1016,7 @@
       <c r="K6" s="1" t="n"/>
       <c r="L6" s="55" t="inlineStr">
         <is>
-          <t>KK주사 설명: 엑셀 D열은 '라쥬니스 줄기세포', PPT 1p는 '라쥬니셀 줄기세포' → 명칭 통일 필요</t>
+          <t>KK주사 설명: 엑셀 D열은 '라쥬니스 줄기세포', PPT 1p는 '라쥬니셀 줄기세포' → 명칭 통일 필요 (번역본도 Lajunicell/Rajunicell/リジュニセル/RAJUNISS로 제각각)</t>
         </is>
       </c>
       <c r="M6" s="1" t="n"/>
